--- a/MPOs/on-prem/bardstown_menu_promos.xlsx
+++ b/MPOs/on-prem/bardstown_menu_promos.xlsx
@@ -1,185 +1,61 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Report" sheetId="1" r:id="rId1"/>
-    <sheet name="Filters" sheetId="2" r:id="rId2"/>
+    <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Filters" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
-  <si>
-    <t>Values were filtered by:</t>
-  </si>
-  <si>
-    <t>Brands</t>
-  </si>
-  <si>
-    <t>BARDSTOWN BOURBON COLLAB SERIES FOURSQUARE, BARDSTOWN BOURBON COLLAB SERIES GOOSE ISLAND</t>
-  </si>
-  <si>
-    <t>Start Date</t>
-  </si>
-  <si>
-    <t>09/01/2026</t>
-  </si>
-  <si>
-    <t>End Date</t>
-  </si>
-  <si>
-    <t>09/02/2026</t>
-  </si>
-  <si>
-    <t>Date/Time</t>
-  </si>
-  <si>
-    <t>Promo #</t>
-  </si>
-  <si>
-    <t>Photo taker</t>
-  </si>
-  <si>
-    <t>District Manager</t>
-  </si>
-  <si>
-    <t>Sales Manager</t>
-  </si>
-  <si>
-    <t>Photo taker's role</t>
-  </si>
-  <si>
-    <t>Promotion type</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>DBA</t>
-  </si>
-  <si>
-    <t>Account #</t>
-  </si>
-  <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>Theme</t>
-  </si>
-  <si>
-    <t>Elements</t>
-  </si>
-  <si>
-    <t>Brand</t>
-  </si>
-  <si>
-    <t>Supplier</t>
-  </si>
-  <si>
-    <t>Photo</t>
-  </si>
-  <si>
-    <t>09/02/2026 09:10 AM</t>
-  </si>
-  <si>
-    <t>1.1</t>
-  </si>
-  <si>
-    <t>robin feldman</t>
-  </si>
-  <si>
-    <t>Christopher McCrohan</t>
-  </si>
-  <si>
-    <t>Sales Rep</t>
-  </si>
-  <si>
-    <t>Feature Activation (on)</t>
-  </si>
-  <si>
-    <t>HILTON HASBRK HTS #50591</t>
-  </si>
-  <si>
-    <t>34018</t>
-  </si>
-  <si>
-    <t>650 TERRACE AVE</t>
-  </si>
-  <si>
-    <t>HASBROUCK HEIGHTS</t>
-  </si>
-  <si>
-    <t>Drink Special</t>
-  </si>
-  <si>
-    <t>Table Tent</t>
-  </si>
-  <si>
-    <t>BARDSTOWN BOURBON COLLAB SERIES FOURSQUARE</t>
-  </si>
-  <si>
-    <t>BARDSTOWN BOURBON COMPANY</t>
-  </si>
-  <si>
-    <t>1.2</t>
-  </si>
-  <si>
-    <t>BARDSTOWN BOURBON COLLAB SERIES GOOSE ISLAND</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="5">
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color rgb="FF0000FF"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -218,31 +94,99 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -530,229 +474,420 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="25.7109375" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" customWidth="1"/>
-    <col min="9" max="9" width="26.7109375" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" customWidth="1"/>
-    <col min="11" max="11" width="17.7109375" customWidth="1"/>
-    <col min="12" max="12" width="19.7109375" customWidth="1"/>
-    <col min="13" max="13" width="15.7109375" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" customWidth="1"/>
-    <col min="15" max="15" width="46.7109375" customWidth="1"/>
-    <col min="16" max="16" width="27.7109375" customWidth="1"/>
-    <col min="17" max="17" width="7.7109375" customWidth="1"/>
+    <col width="21.7109375" customWidth="1" style="6" min="1" max="1"/>
+    <col width="9.7109375" customWidth="1" style="6" min="2" max="2"/>
+    <col width="15.7109375" customWidth="1" style="6" min="3" max="3"/>
+    <col width="22.7109375" customWidth="1" style="6" min="4" max="4"/>
+    <col width="15.7109375" customWidth="1" style="6" min="5" max="5"/>
+    <col width="20.7109375" customWidth="1" style="6" min="6" max="6"/>
+    <col width="25.7109375" customWidth="1" style="6" min="7" max="7"/>
+    <col width="10.7109375" customWidth="1" style="6" min="8" max="8"/>
+    <col width="26.7109375" customWidth="1" style="6" min="9" max="9"/>
+    <col width="11.7109375" customWidth="1" style="6" min="10" max="10"/>
+    <col width="17.7109375" customWidth="1" style="6" min="11" max="11"/>
+    <col width="19.7109375" customWidth="1" style="6" min="12" max="12"/>
+    <col width="15.7109375" customWidth="1" style="6" min="13" max="13"/>
+    <col width="12.7109375" customWidth="1" style="6" min="14" max="14"/>
+    <col width="46.7109375" customWidth="1" style="6" min="15" max="15"/>
+    <col width="27.7109375" customWidth="1" style="6" min="16" max="16"/>
+    <col width="7.7109375" customWidth="1" style="6" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
-      <c r="A1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>23</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date/Time</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Promo #</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Photo taker</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>District Manager</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Photo taker's role</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Promotion type</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Account #</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Theme</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Elements</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:17">
-      <c r="A2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" s="2">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>09/09/2026 04:48 PM</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>allison scott</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Christopher McCrohan</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Cocktail List Activation</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>BLACKJACK MULLIGAN'S PUBLIC HOUSE</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>15004</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>1145 MCBRIDE AVE</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>WOODLAND PARK</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>GREEN RIVER KENTUCKY STRAIGHT WHEATED BOURBON WHISKEY</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>BARDSTOWN BOURBON COMPANY</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>09/02/2026 09:10 AM</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>robin feldman</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Christopher McCrohan</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation (on)</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>23</v>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>HILTON HASBRK HTS #50591</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>34018</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>650 TERRACE AVE</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>HASBROUCK HEIGHTS</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Drink Special</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Table Tent</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>BARDSTOWN BOURBON COLLAB SERIES FOURSQUARE</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>BARDSTOWN BOURBON COMPANY</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:17">
-      <c r="A3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="2">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>09/02/2026 09:10 AM</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>robin feldman</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Christopher McCrohan</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation (on)</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>23</v>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>HILTON HASBRK HTS #50591</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>34018</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>650 TERRACE AVE</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>HASBROUCK HEIGHTS</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Drink Special</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Table Tent</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>BARDSTOWN BOURBON COLLAB SERIES GOOSE ISLAND</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>BARDSTOWN BOURBON COMPANY</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="Q2" r:id="rId1"/>
-    <hyperlink ref="Q3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="50.7109375" customWidth="1"/>
+    <col width="50.7109375" customWidth="1" style="6" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4"/>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Values were filtered by:</t>
+        </is>
+      </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Brands</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>BARDSTOWN BOURBON COLLAB SERIES FOURSQUARE, BARDSTOWN BOURBON COLLAB SERIES GOOSE ISLAND</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Start Date</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>09/01/2026</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>End Date</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>09/02/2026</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/MPOs/on-prem/bardstown_menu_promos.xlsx
+++ b/MPOs/on-prem/bardstown_menu_promos.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.7109375" customWidth="1" style="6" min="1" max="1"/>
@@ -591,17 +591,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09/09/2026 04:48 PM</t>
+          <t>09/11/2026 08:53 AM</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>allison scott</t>
+          <t>Nicholas Melissari</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -623,33 +623,33 @@
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>BLACKJACK MULLIGAN'S PUBLIC HOUSE</t>
+          <t>NEW PARK TAV (A)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>15004</t>
+          <t>31027</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>1145 MCBRIDE AVE</t>
+          <t>250 PARK AVE</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>WOODLAND PARK</t>
+          <t>EAST RUTHERFORD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Menu</t>
+          <t>Table Tent, Menu</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>GREEN RIVER KENTUCKY STRAIGHT WHEATED BOURBON WHISKEY</t>
+          <t>GREEN RIVER HONEY FINISHED BOURBON</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -666,17 +666,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09/02/2026 09:10 AM</t>
+          <t>09/11/2026 08:51 AM</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>robin feldman</t>
+          <t>Nicholas Melissari</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Feature Activation (on)</t>
+          <t>Feature Activation</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
@@ -700,37 +700,29 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>HILTON HASBRK HTS #50591</t>
+          <t>RED BULL VENDING MACHINE</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>34018</t>
+          <t>120001</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>650 TERRACE AVE</t>
+          <t>150 WAGARAW RD</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>HASBROUCK HEIGHTS</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Drink Special</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Table Tent</t>
-        </is>
-      </c>
+          <t>HAWTHORNE</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>BARDSTOWN BOURBON COLLAB SERIES FOURSQUARE</t>
+          <t>GREEN RIVER HONEY FINISHED BOURBON</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -747,17 +739,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>09/02/2026 09:10 AM</t>
+          <t>09/09/2026 04:48 PM</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>robin feldman</t>
+          <t>allison scott</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -773,53 +765,209 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>Cocktail List Activation</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>BLACKJACK MULLIGAN'S PUBLIC HOUSE</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>15004</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1145 MCBRIDE AVE</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>WOODLAND PARK</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>GREEN RIVER KENTUCKY STRAIGHT WHEATED BOURBON WHISKEY</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>BARDSTOWN BOURBON COMPANY</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>09/02/2026 09:10 AM</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>robin feldman</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Christopher McCrohan</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>Feature Activation (on)</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>HILTON HASBRK HTS #50591</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>34018</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>650 TERRACE AVE</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>HASBROUCK HEIGHTS</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>Drink Special</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>Table Tent</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>BARDSTOWN BOURBON COLLAB SERIES FOURSQUARE</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>BARDSTOWN BOURBON COMPANY</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>Photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>09/02/2026 09:10 AM</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>robin feldman</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Christopher McCrohan</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Sales Rep</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Feature Activation (on)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>HILTON HASBRK HTS #50591</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>34018</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>650 TERRACE AVE</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>HASBROUCK HEIGHTS</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Drink Special</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Table Tent</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>BARDSTOWN BOURBON COLLAB SERIES GOOSE ISLAND</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>BARDSTOWN BOURBON COMPANY</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>Photo</t>
         </is>
@@ -830,6 +978,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -886,7 +1036,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>09/02/2026</t>
+          <t>09/11/2026</t>
         </is>
       </c>
     </row>
